--- a/data/trans_orig/IQ2608_R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ2608_R3-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88051</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81390</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>93555</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>67867</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>60821</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>73958</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>60328</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>73816</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>75,19%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>81,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>88051</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>81826</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>94152</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145740</t>
+          <t>147107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164544</t>
+          <t>164705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17897</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24558</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22394</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16303</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29440</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16445</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29933</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>24,81%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17897</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11796</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24122</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31664</t>
+          <t>31503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50468</t>
+          <t>49101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>105948</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>105948</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>105948</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90261</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90261</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90261</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>105948</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>105948</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>105948</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>172900</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>160761</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>184110</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>63,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>168419</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>156173</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>179935</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>155275</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>180061</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>66,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>172900</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>159901</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>183960</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>68,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>324775</t>
+          <t>324127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358421</t>
+          <t>358306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80856</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69646</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92995</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>84338</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72822</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>96584</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>72696</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>97482</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>33,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>80856</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>69796</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>93855</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148093</t>
+          <t>148208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181739</t>
+          <t>182387</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252757</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252757</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252757</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87956</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>78388</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>96840</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>55,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>61057</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>52474</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>70164</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>51478</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>70360</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>47,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>87956</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>78033</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>96852</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>62,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135722</t>
+          <t>136886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162699</t>
+          <t>162493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53559</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>44675</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>63127</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66491</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57384</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>75074</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57188</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76070</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>52,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>58,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>53559</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>44663</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>63482</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,85%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106364</t>
+          <t>106570</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133341</t>
+          <t>132177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>100605</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>89433</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>112670</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>48,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>105330</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>93427</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>115920</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>94236</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>116035</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>54,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,13%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>100605</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>88667</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>111285</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>48,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190196</t>
+          <t>189504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220637</t>
+          <t>223095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105444</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>93379</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116616</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>88767</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>78177</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>100670</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>78062</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>99861</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>45,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105444</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>94764</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>117382</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179509</t>
+          <t>177051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209950</t>
+          <t>210642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>449512</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>427713</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>469268</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>402674</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>382463</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>421897</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>383130</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>422022</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>60,58%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>449512</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>430161</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>470967</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>824752</t>
+          <t>821846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>881865</t>
+          <t>881029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>257756</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>238000</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>279555</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>386</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>261989</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>242766</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>282200</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>242641</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>281533</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>257756</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>236301</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>277107</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>490065</t>
+          <t>490901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>547178</t>
+          <t>550084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>108596</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>103302</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>112773</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>87,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>113563</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>107172</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>118499</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>107712</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>118069</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>90,35%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>85,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>108596</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>103383</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>112802</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214018</t>
+          <t>213777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>228801</t>
+          <t>228140</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9979</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15273</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12127</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7191</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18518</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7621</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17978</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>9,65%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9979</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5773</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15192</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>125690</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>125690</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>125690</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>233612</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>223612</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>242690</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>86,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>206796</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>197736</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>213957</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>197444</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>214259</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>87,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>83,7%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>233612</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>223998</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>242771</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>426309</t>
+          <t>427812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>453312</t>
+          <t>453149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35379</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26301</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>45379</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>29454</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22293</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38514</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21991</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38806</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>12,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35379</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>26220</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>44993</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51929</t>
+          <t>52092</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78932</t>
+          <t>77429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3361,67 +3361,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>117204</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>107315</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>126509</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>120988</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>111996</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>129623</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>112325</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>129325</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>77,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>82,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>117204</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>108274</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>126479</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,91%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225418</t>
+          <t>225401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250589</t>
+          <t>251135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41367</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32062</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>51256</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>32,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>35446</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26811</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>44438</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27109</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>44109</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>22,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>41367</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>32092</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>50297</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,09%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64416</t>
+          <t>63870</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89587</t>
+          <t>89604</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>134807</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>125225</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>144969</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>116384</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>105763</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125799</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>106692</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>125378</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,93%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>134807</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>124535</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>143293</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>74,91%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>237449</t>
+          <t>237696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>264183</t>
+          <t>266145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45148</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34986</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54730</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>54953</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45538</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>65574</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>45959</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>64645</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,07%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>45148</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>36662</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>55420</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>25,09%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>85147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113843</t>
+          <t>113596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>594219</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>576562</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>609777</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>79,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>83,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>557731</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>541099</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>574532</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>538893</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>573373</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>80,86%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>594219</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>575995</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>611031</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1126863</t>
+          <t>1127254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1176791</t>
+          <t>1176340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>131873</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>116315</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>149530</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>131980</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>115179</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>148612</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>116338</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>150818</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>19,14%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>131873</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>115061</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>150097</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>18,16%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239012</t>
+          <t>239463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288940</t>
+          <t>288549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>95642</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>87675</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>101459</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>81,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>94883</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>86618</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>101718</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>86454</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>100994</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>78,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>71,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>95642</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>88439</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>101377</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>81,99%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>181261</t>
+          <t>181053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>200812</t>
+          <t>199522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21009</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15192</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28976</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25940</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19105</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34205</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19829</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34369</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>28,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21009</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15274</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28212</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36662</t>
+          <t>37952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56213</t>
+          <t>56421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,107 +4960,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>223146</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>212797</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>230746</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>86,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>82,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>89,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>186282</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>178101</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>193524</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>178538</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>192828</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>88,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>84,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>223146</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>213498</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>231676</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>86,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>91,6%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>409428</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>397188</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>420704</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>87,38%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>84,76%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>89,78%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>409428</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>398227</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>420743</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>87,38%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>84,99%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -5073,107 +5073,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34915</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27315</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>45264</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>24235</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16993</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32416</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17689</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>31979</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>11,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>34915</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>26385</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>44563</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>59150</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>47874</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>71390</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>12,62%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>10,22%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>59150</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>47835</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>70351</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>12,62%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>151487</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>141650</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>160524</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>80,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>75,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>149721</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>139329</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>158324</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>139204</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>157472</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>79,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>151487</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>140935</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>160147</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>80,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288219</t>
+          <t>287963</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313151</t>
+          <t>314072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37085</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28048</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>46922</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>39178</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30575</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49570</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>31427</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>49695</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>20,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37085</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28425</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>47637</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64320</t>
+          <t>63399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89252</t>
+          <t>89508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>143521</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>133516</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>150996</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82,46%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>76,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>127483</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>117806</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>136624</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>116989</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>136248</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>143521</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>134984</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>150822</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257108</t>
+          <t>257178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282638</t>
+          <t>282762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30527</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23052</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40532</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>45818</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36677</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>55495</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37053</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>56312</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30527</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>23226</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39064</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64710</t>
+          <t>64586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90240</t>
+          <t>90170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>613797</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>596134</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>629014</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>80,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>85,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>845</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>558368</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>541123</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>574331</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>540588</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>573493</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>80,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>82,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>613797</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>597211</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>631168</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1148659</t>
+          <t>1149605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1195316</t>
+          <t>1195652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>123535</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>108318</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>141198</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,75%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>135172</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>119209</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>152417</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>120047</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>152952</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>19,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>123535</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>106164</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>140121</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235555</t>
+          <t>235219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>282212</t>
+          <t>281266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1043</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,74 +6564,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7921</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12620</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9358</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11691</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8689</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12729</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>68,26%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13163</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10175</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14310</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>71,1%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23067</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>957</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28511</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23564</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32826</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,22%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>83,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24546</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19906</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28159</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>71,48%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>57,97%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>82,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32505</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26984</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36929</t>
+          <t>24431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>57052</t>
+          <t>49812</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50070</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>55701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>10968</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14434</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>13335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29034</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36778</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30327</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42739</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>69,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24662</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18872</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30139</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>61,64%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>22957</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31740</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44642</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>63194</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53693</t>
+          <t>51523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71116</t>
+          <t>67631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10554</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22966</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15345</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9868</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21135</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38,36%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24177</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>32730</t>
+          <t>32014</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42231</t>
+          <t>40226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>46458</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38941</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54606</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>62,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>73,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31388</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>25297</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>37386</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>57,07%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>46,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48307</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40395</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56304</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>79695</t>
+          <t>79616</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68608</t>
+          <t>67946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88917</t>
+          <t>89967</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23606</t>
+          <t>27968</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28472</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>18503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>31215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>52563</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42856</t>
+          <t>42212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63165</t>
+          <t>64233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>54994</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54994</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>54994</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57752</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131773</t>
+          <t>132179</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131773</t>
+          <t>132179</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131773</t>
+          <t>132179</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>121957</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>110250</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>133410</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>93216</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>83202</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>101927</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>58,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>132508</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120350</t>
+          <t>79324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>97910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>211062</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210701</t>
+          <t>195323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>241588</t>
+          <t>225383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>56408</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44955</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>68115</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>49877</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>41166</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>59891</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59262</t>
+          <t>50428</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71420</t>
+          <t>60210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>109139</t>
+          <t>106837</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93275</t>
+          <t>92516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124162</t>
+          <t>122576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
